--- a/Output Files GPT-OSS 20B/rag_ablation_summary.xlsx
+++ b/Output Files GPT-OSS 20B/rag_ablation_summary.xlsx
@@ -496,42 +496,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>control_k3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
+          <t>Control k=3 standard</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>1.325175925925926</v>
+        <v>4.075333333333333</v>
       </c>
       <c r="E2" t="n">
-        <v>1.384102088548924</v>
+        <v>4.24144935268473</v>
       </c>
       <c r="F2" t="n">
-        <v>0.816496580927726</v>
+        <v>0.3333333333333334</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8660254037844387</v>
+        <v>0.5</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>0.06848494191136625</v>
+        <v>0.08224670340617499</v>
       </c>
       <c r="K2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
